--- a/test/integration/rotor/01.xlsx
+++ b/test/integration/rotor/01.xlsx
@@ -351,12 +351,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>variable</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>coefficient</t>
         </is>
       </c>
     </row>
@@ -2215,17 +2215,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>constraint</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Relation</t>
+          <t>relation</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>RHS</t>
+          <t>rhs</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
